--- a/questionnaire_templates/017_research_hypothesis_evaluation_form--questionnaire_templates.xlsx
+++ b/questionnaire_templates/017_research_hypothesis_evaluation_form--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>research_hypothesis</t>
+          <t>research_hypothesis_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Research Background</t>
+          <t>Research Background (2)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -616,12 +616,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>research_hypothesis</t>
+          <t>research_hypothesis_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Research Hypothesis</t>
+          <t>Research Hypothesis 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -777,12 +777,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>review_date</t>
+          <t>review_date_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Review Date</t>
+          <t>Review Date 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -800,12 +800,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>research_hypothesis</t>
+          <t>research_hypothesis_4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Research Hypothesis</t>
+          <t>Research Hypothesis 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -823,12 +823,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>research_background</t>
+          <t>research_background_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Research Background</t>
+          <t>Research Background (3)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
